--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -886,38 +886,30 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>46372200</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>36600</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K5" s="5" t="n">
+        <v>46372200</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>36600</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -926,7 +918,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40724,7 +40716,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40734,7 +40726,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40789,12 +40781,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
+$4637万
+$36,600/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -119,13 +119,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -948,38 +948,30 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>48246600</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>38200</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="5" t="n">
+        <v>48246600</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>38200</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -988,7 +980,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40716,7 +40708,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40726,7 +40718,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40774,6 +40766,357 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4825万
+$38,200/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4637万
+$36,600/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2634万
+$26,187/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2687万
+$27,906/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4624万
+$36,615/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4358万
+$34,400/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2621万
+$26,056/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2661万
+$27,630/呎
+(24年-05月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4408万
+$34,900/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4434万
+$35,000/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2608万
+$25,928/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2634万
+$27,355/呎
+(24年-05月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4231万
+$33,500/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4080万
+$32,200/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2595万
+$25,798/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2716万
+$28,200/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4181万
+$33,100/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4029万
+$31,800/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2561万
+$25,456/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2582万
+$26,817/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4130万
+$32,700/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3978万
+$31,400/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2536万
+$25,205/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2662万
+$27,645/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4092万
+$32,400/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3940万
+$31,100/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2523万
+$25,080/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2596万
+$26,952/呎
+(24年-04月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3821万
+$30,250/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3978万
+$31,400/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2510万
+$24,953/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2583万
+$26,818/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3769万
+$29,842/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4029万
+$31,800/呎
+(26年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2488万
+$24,727/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2570万
+$26,685/呎
+(24年-04月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
 招标单位
@@ -40781,350 +41124,272 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$4637万
-$36,600/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
+$3953万
+$31,200/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2634万
-$26,187/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+$2475万
+$24,602/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2687万
-$27,906/呎
+$2557万
+$26,552/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3886万
+$30,764/呎
+(24年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3928万
+$31,000/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2463万
+$24,480/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2444万
+$25,375/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3866万
+$30,610/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3902万
+$30,800/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2450万
+$24,359/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2532万
+$26,288/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3847万
+$30,458/呎
+(24年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3890万
+$30,700/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2342万
+$23,278/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2508万
+$26,049/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3828万
+$30,308/呎
+(24年-05月-09日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2422万
+$24,077/呎
 (24年-05月-03日)</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2496万
+$25,920/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-$4624万
-$36,615/呎
-(26年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
+$3663万
+$29,006/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$4358万
-$34,400/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
+$3961万
+$31,259/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2621万
-$26,056/呎
+$2410万
+$23,956/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2386万
+$24,772/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1264呎 (4+房)
+$3804万
+$30,093/呎
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2303万
+$22,895/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2661万
-$27,630/呎
-(24年-05月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4408万
-$34,900/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4434万
-$35,000/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2608万
-$25,928/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2634万
-$27,355/呎
-(24年-05月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4231万
-$33,500/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4080万
-$32,200/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2595万
-$25,798/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2716万
-$28,200/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4181万
-$33,100/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4029万
-$31,800/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2561万
-$25,456/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2582万
-$26,817/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4130万
-$32,700/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3978万
-$31,400/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2536万
-$25,205/呎
+$2471万
+$25,663/呎
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2662万
-$27,645/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4092万
-$32,400/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3940万
-$31,100/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2523万
-$25,080/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2596万
-$26,952/呎
-(24年-04月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3821万
-$30,250/呎
-(24年-05月-23日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3978万
-$31,400/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2510万
-$24,953/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2583万
-$26,818/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3769万
-$29,842/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4029万
-$31,800/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2488万
-$24,727/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2570万
-$26,685/呎
-(24年-04月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
 招标单位
@@ -41132,163 +41397,202 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$3953万
-$31,200/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+$3750万
+$29,600/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2475万
-$24,602/呎
+$2292万
+$22,781/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2459万
+$25,536/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3766万
+$29,819/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3725万
+$29,400/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2358万
+$23,441/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2447万
+$25,408/呎
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3747万
+$29,671/呎
+(24年-05月-31日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3712万
+$29,300/呎
+(26年-03月-26日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2347万
+$23,326/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2557万
-$26,552/呎
+$2338万
+$24,282/呎
 (24年-04月-26日)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-$3886万
-$30,764/呎
-(24年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$3720万
+$29,450/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1238呎 (4+房)
+$3677万
+$29,700/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2335万
+$23,209/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2462万
+$25,564/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3827万
+$30,300/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$3928万
-$31,000/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+$3776万
+$29,800/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2463万
-$24,480/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$2323万
+$23,093/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2444万
-$25,375/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
+$2437万
+$25,309/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-$3866万
-$30,610/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3902万
+$3890万
 $30,800/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2450万
-$24,359/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2532万
-$26,288/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3847万
-$30,458/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3890万
-$30,700/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2342万
-$23,278/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2508万
-$26,049/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3828万
-$30,308/呎
-(24年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
 招标单位
@@ -41296,77 +41600,77 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2422万
-$24,077/呎
+$2312万
+$22,979/呎
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2496万
-$25,920/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+$2425万
+$25,183/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-$3663万
-$29,006/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+$3814万
+$30,200/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$3961万
-$31,259/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+$3636万
+$28,700/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2410万
-$23,956/呎
+$2209万
+$21,960/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2413万
+$25,058/呎
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2386万
-$24,772/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 1264呎 (4+房)
-$3804万
-$30,093/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3802万
+$30,100/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
 招标单位
@@ -41374,30 +41678,108 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2303万
-$22,895/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$2279万
+$22,655/呎
+(24年-04月-06日)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2471万
-$25,663/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+$2401万
+$24,933/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3776万
+$29,900/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2268万
+$22,542/呎
+(24年-05月-02日)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2389万
+$24,809/呎
+(24年-04月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3776万
+$29,900/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2245万
+$22,319/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2377万
+$24,685/呎
+(24年-05月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
 招标单位
@@ -41405,202 +41787,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3750万
-$29,600/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2292万
-$22,781/呎
-(24年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2459万
-$25,536/呎
-(24年-04月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3766万
-$29,819/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3725万
-$29,400/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2358万
-$23,441/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2447万
-$25,408/呎
-(24年-04月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3747万
-$29,671/呎
-(24年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3712万
-$29,300/呎
-(26年-03月-26日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2347万
-$23,326/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2338万
-$24,282/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3720万
-$29,450/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 1238呎 (4+房)
-$3677万
-$29,700/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2335万
-$23,209/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2462万
-$25,564/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3827万
-$30,300/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3776万
-$29,800/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2323万
-$23,093/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2437万
-$25,309/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3890万
-$30,800/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
 招标单位
@@ -41608,77 +41795,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
-$2312万
-$22,979/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$2223万
+$22,096/呎
+(24年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
-$2425万
-$25,183/呎
+$2260万
+$23,474/呎
 (24年-05月-08日)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-$3814万
-$30,200/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3636万
-$28,700/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2209万
-$21,960/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2413万
-$25,058/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3802万
-$30,100/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
+$3776万
+$29,900/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
 招标单位
@@ -41686,163 +41834,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2279万
-$22,655/呎
-(24年-04月-06日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2401万
-$24,933/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3776万
-$29,900/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2268万
-$22,542/呎
-(24年-05月-02日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2389万
-$24,809/呎
-(24年-04月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3776万
-$29,900/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2245万
-$22,319/呎
-(24年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2377万
-$24,685/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2223万
-$22,096/呎
-(24年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2260万
-$23,474/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3776万
-$29,900/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
 $2179万
@@ -41850,7 +41842,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 963呎 (3房)
 $2314万
@@ -41865,7 +41857,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 1226呎 (4+房)
 $3984万
@@ -41873,7 +41865,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 1229呎 (4+房)
 招标单位
@@ -41881,7 +41873,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 1006呎 (3房)
 $2137万
@@ -41889,7 +41881,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 938呎 (3房)
 $2466万
@@ -42027,7 +42019,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2574万
@@ -42035,7 +42027,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2579万
@@ -42043,7 +42035,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2490万
@@ -42051,7 +42043,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2758万
@@ -42066,7 +42058,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2542万
@@ -42074,7 +42066,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2566万
@@ -42082,7 +42074,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2461万
@@ -42090,7 +42082,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2634万
@@ -42105,7 +42097,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2515万
@@ -42113,7 +42105,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2554万
@@ -42121,7 +42113,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2433万
@@ -42129,7 +42121,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2716万
@@ -42144,7 +42136,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2482万
@@ -42152,7 +42144,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2440万
@@ -42160,7 +42152,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2408万
@@ -42168,7 +42160,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2677万
@@ -42183,7 +42175,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2449万
@@ -42191,7 +42183,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2426万
@@ -42199,7 +42191,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2397万
@@ -42207,7 +42199,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2514万
@@ -42222,7 +42214,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2321万
@@ -42230,7 +42222,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2404万
@@ -42238,7 +42230,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2373万
@@ -42246,7 +42238,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2570万
@@ -42261,7 +42253,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2401万
@@ -42269,7 +42261,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2489万
@@ -42277,7 +42269,7 @@
 (24年-06月-21日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2361万
@@ -42285,7 +42277,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2410万
@@ -42300,7 +42292,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2283万
@@ -42308,7 +42300,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2476万
@@ -42316,7 +42308,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2349万
@@ -42324,7 +42316,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2497万
@@ -42339,7 +42331,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2354万
@@ -42347,7 +42339,7 @@
 (24年-04月-06日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2464万
@@ -42355,7 +42347,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2338万
@@ -42363,7 +42355,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2386万
@@ -42378,7 +42370,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2342万
@@ -42386,7 +42378,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2452万
@@ -42394,7 +42386,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2326万
@@ -42402,7 +42394,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2472万
@@ -42417,7 +42409,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2330万
@@ -42425,7 +42417,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2340万
@@ -42433,7 +42425,7 @@
 (24年-05月-20日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2314万
@@ -42441,7 +42433,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2460万
@@ -42456,7 +42448,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2319万
@@ -42464,7 +42456,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2424万
@@ -42472,7 +42464,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2303万
@@ -42480,7 +42472,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2441万
@@ -42495,7 +42487,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2307万
@@ -42503,7 +42495,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2316万
@@ -42511,7 +42503,7 @@
 (24年-05月-23日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2201万
@@ -42519,7 +42511,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2429万
@@ -42534,7 +42526,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2296万
@@ -42542,7 +42534,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2400万
@@ -42550,7 +42542,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2280万
@@ -42558,7 +42550,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2417万
@@ -42573,7 +42565,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2284万
@@ -42581,7 +42573,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2293万
@@ -42589,7 +42581,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2269万
@@ -42597,7 +42589,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2405万
@@ -42612,7 +42604,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2273万
@@ -42620,7 +42612,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2376万
@@ -42628,7 +42620,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2168万
@@ -42636,7 +42628,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2393万
@@ -42651,7 +42643,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2262万
@@ -42659,7 +42651,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2271万
@@ -42667,7 +42659,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2246万
@@ -42675,7 +42667,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2379万
@@ -42690,7 +42682,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2250万
@@ -42698,7 +42690,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2352万
@@ -42706,7 +42698,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2235万
@@ -42714,7 +42706,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2274万
@@ -42729,7 +42721,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2239万
@@ -42737,7 +42729,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2341万
@@ -42745,7 +42737,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2224万
@@ -42753,7 +42745,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2262万
@@ -42768,7 +42760,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2228万
@@ -42776,7 +42768,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2234万
@@ -42784,7 +42776,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2213万
@@ -42792,7 +42784,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2344万
@@ -42807,7 +42799,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2206万
@@ -42815,7 +42807,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2314万
@@ -42823,7 +42815,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2576万
@@ -42831,7 +42823,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2240万
@@ -42846,7 +42838,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2108万
@@ -42854,7 +42846,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2303万
@@ -42862,7 +42854,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2191万
@@ -42870,7 +42862,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2727万
@@ -42885,7 +42877,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2184万
@@ -42893,7 +42885,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2291万
@@ -42901,7 +42893,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2180万
@@ -42909,7 +42901,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2309万
@@ -42924,7 +42916,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2087万
@@ -42932,7 +42924,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2280万
@@ -42940,7 +42932,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2172万
@@ -42948,7 +42940,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2298万
@@ -42963,7 +42955,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2162万
@@ -42971,7 +42963,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2265万
@@ -42979,7 +42971,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2164万
@@ -42987,7 +42979,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2286万
@@ -43002,7 +42994,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2152万
@@ -43010,7 +43002,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2243万
@@ -43018,7 +43010,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2057万
@@ -43026,7 +43018,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2275万
@@ -43041,7 +43033,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2130万
@@ -43049,7 +43041,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2133万
@@ -43057,7 +43049,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2037万
@@ -43065,7 +43057,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2252万
@@ -43080,7 +43072,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2109万
@@ -43088,7 +43080,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2175万
@@ -43096,7 +43088,7 @@
 (24年-05月-24日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2095万
@@ -43104,7 +43096,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2142万
@@ -43119,7 +43111,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 958呎 (3房)
 $2237万
@@ -43127,7 +43119,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
 $2367万
@@ -43135,7 +43127,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 972呎 (3房)
 $2157万
@@ -43143,7 +43135,7 @@
 (24年-04月-13日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 972呎 (3房)
 $2186万
@@ -43293,7 +43285,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2027万
@@ -43301,7 +43293,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2212万
@@ -43309,7 +43301,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1881万
@@ -43317,7 +43309,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $2008万
@@ -43325,7 +43317,7 @@
 (26年-03月-18日)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1951万
@@ -43333,7 +43325,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $2100万
@@ -43348,7 +43340,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2012万
@@ -43356,7 +43348,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2068万
@@ -43364,7 +43356,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1865万
@@ -43372,7 +43364,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1988万
@@ -43380,7 +43372,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1849万
@@ -43388,7 +43380,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $2080万
@@ -43403,7 +43395,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1987万
@@ -43411,7 +43403,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2130万
@@ -43419,7 +43411,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1849万
@@ -43427,7 +43419,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1978万
@@ -43435,7 +43427,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1898万
@@ -43443,7 +43435,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1969万
@@ -43458,7 +43450,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2058万
@@ -43466,7 +43458,7 @@
 (24年-04月-06日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2120万
@@ -43474,7 +43466,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1830万
@@ -43482,7 +43474,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1968万
@@ -43490,7 +43482,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1870万
@@ -43498,7 +43490,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $2027万
@@ -43513,7 +43505,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2034万
@@ -43521,7 +43513,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2038万
@@ -43529,7 +43521,7 @@
 (24年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1745万
@@ -43537,7 +43529,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1958万
@@ -43545,7 +43537,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1847万
@@ -43553,7 +43545,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $2002万
@@ -43568,7 +43560,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2026万
@@ -43576,7 +43568,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2025万
@@ -43584,7 +43576,7 @@
 (24年-06月-17日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1736万
@@ -43592,7 +43584,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1949万
@@ -43600,7 +43592,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1756万
@@ -43608,7 +43600,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1973万
@@ -43623,7 +43615,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2023万
@@ -43631,7 +43623,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1925万
@@ -43639,7 +43631,7 @@
 (24年-05月-23日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1790万
@@ -43647,7 +43639,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $2075万
@@ -43655,7 +43647,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1811万
@@ -43663,7 +43655,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1954万
@@ -43678,7 +43670,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1934万
@@ -43686,7 +43678,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1995万
@@ -43694,7 +43686,7 @@
 (24年-05月-23日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1781万
@@ -43702,7 +43694,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1969万
@@ -43710,7 +43702,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1802万
@@ -43718,7 +43710,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1928万
@@ -43733,7 +43725,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $2003万
@@ -43741,7 +43733,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2085万
@@ -43749,7 +43741,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1772万
@@ -43757,7 +43749,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1906万
@@ -43765,7 +43757,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1793万
@@ -43773,7 +43765,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1834万
@@ -43788,7 +43780,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1914万
@@ -43796,7 +43788,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2075万
@@ -43804,7 +43796,7 @@
 (26年-03月-23日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1763万
@@ -43812,7 +43804,7 @@
 (24年-04月-06日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1896万
@@ -43820,7 +43812,7 @@
 (26年-03月-23日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1713万
@@ -43828,7 +43820,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1810万
@@ -43843,7 +43835,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1983万
@@ -43851,7 +43843,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1887万
@@ -43859,7 +43851,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1754万
@@ -43867,7 +43859,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1879万
@@ -43875,7 +43867,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1705万
@@ -43883,7 +43875,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1784万
@@ -43898,7 +43890,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1973万
@@ -43906,7 +43898,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2009万
@@ -43914,7 +43906,7 @@
 (24年-08月-05日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1746万
@@ -43922,7 +43914,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1870万
@@ -43930,7 +43922,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1766万
@@ -43938,7 +43930,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1849万
@@ -43953,7 +43945,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1964万
@@ -43961,7 +43953,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1864万
@@ -43969,7 +43961,7 @@
 (24年-05月-16日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1972万
@@ -43977,7 +43969,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1861万
@@ -43985,7 +43977,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1757万
@@ -43993,7 +43985,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1839万
@@ -44008,7 +44000,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1954万
@@ -44016,7 +44008,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1855万
@@ -44024,7 +44016,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1728万
@@ -44032,7 +44024,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1735万
@@ -44040,7 +44032,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1749万
@@ -44048,7 +44040,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1830万
@@ -44063,7 +44055,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1867万
@@ -44071,7 +44063,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1921万
@@ -44079,7 +44071,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1720万
@@ -44087,7 +44079,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1842万
@@ -44095,7 +44087,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1740万
@@ -44103,7 +44095,7 @@
 (24年-04月-19日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1821万
@@ -44118,7 +44110,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1934万
@@ -44126,7 +44118,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1834万
@@ -44134,7 +44126,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1711万
@@ -44142,7 +44134,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1833万
@@ -44150,7 +44142,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1731万
@@ -44158,7 +44150,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1812万
@@ -44173,7 +44165,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1925万
@@ -44181,7 +44173,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1900万
@@ -44189,7 +44181,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1636万
@@ -44197,7 +44189,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1709万
@@ -44205,7 +44197,7 @@
 (24年-08月-16日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1723万
@@ -44213,7 +44205,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1803万
@@ -44228,7 +44220,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1907万
@@ -44236,7 +44228,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1815万
@@ -44244,7 +44236,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1694万
@@ -44252,7 +44244,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1701万
@@ -44260,7 +44252,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1714万
@@ -44268,7 +44260,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1794万
@@ -44283,7 +44275,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1826万
@@ -44291,7 +44283,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1881万
@@ -44299,7 +44291,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1686万
@@ -44307,7 +44299,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1762万
@@ -44315,7 +44307,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1638万
@@ -44323,7 +44315,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1785万
@@ -44338,7 +44330,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1808万
@@ -44346,7 +44338,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1871万
@@ -44354,7 +44346,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1678万
@@ -44362,7 +44354,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1753万
@@ -44370,7 +44362,7 @@
 (24年-04月-13日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1689万
@@ -44378,7 +44370,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1767万
@@ -44393,7 +44385,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1798万
@@ -44401,7 +44393,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1858万
@@ -44409,7 +44401,7 @@
 (24年-05月-21日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1920万
@@ -44417,7 +44409,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1708万
@@ -44425,7 +44417,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1680万
@@ -44433,7 +44425,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1759万
@@ -44448,7 +44440,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1786万
@@ -44456,7 +44448,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1848万
@@ -44464,7 +44456,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1661万
@@ -44472,7 +44464,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1700万
@@ -44480,7 +44472,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1606万
@@ -44488,7 +44480,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1750万
@@ -44503,7 +44495,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1778万
@@ -44511,7 +44503,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1766万
@@ -44519,7 +44511,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1653万
@@ -44527,7 +44519,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1691万
@@ -44535,7 +44527,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1664万
@@ -44543,7 +44535,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1959万
@@ -44558,7 +44550,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1761万
@@ -44566,7 +44558,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1830万
@@ -44574,7 +44566,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1581万
@@ -44582,7 +44574,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1616万
@@ -44590,7 +44582,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1657万
@@ -44598,7 +44590,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1949万
@@ -44613,7 +44605,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1832万
@@ -44621,7 +44613,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1749万
@@ -44629,7 +44621,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1638万
@@ -44637,7 +44629,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1674万
@@ -44645,7 +44637,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1650万
@@ -44653,7 +44645,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1724万
@@ -44668,7 +44660,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1751万
@@ -44676,7 +44668,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1812万
@@ -44684,7 +44676,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1630万
@@ -44692,7 +44684,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1666万
@@ -44700,7 +44692,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1641万
@@ -44708,7 +44700,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1716万
@@ -44723,7 +44715,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1814万
@@ -44731,7 +44723,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $2026万
@@ -44739,7 +44731,7 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1620万
@@ -44747,7 +44739,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1650万
@@ -44755,7 +44747,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1633万
@@ -44763,7 +44755,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1707万
@@ -44778,7 +44770,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1796万
@@ -44786,7 +44778,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1714万
@@ -44794,7 +44786,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1608万
@@ -44802,7 +44794,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1576万
@@ -44810,7 +44802,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1623万
@@ -44818,7 +44810,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1690万
@@ -44833,7 +44825,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1778万
@@ -44841,7 +44833,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1763万
@@ -44849,7 +44841,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1600万
@@ -44857,7 +44849,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1625万
@@ -44865,7 +44857,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1611万
@@ -44873,7 +44865,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1673万
@@ -44888,7 +44880,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 773呎 (3房)
 $1943万
@@ -44896,7 +44888,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
 $1728万
@@ -44904,7 +44896,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 747呎 (3房)
 $1706万
@@ -44912,7 +44904,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 728呎 (3房)
 $1536万
@@ -44920,7 +44912,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 737呎 (3房)
 $1669万
@@ -44928,7 +44920,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 748呎 (3房)
 $1777万
@@ -45090,7 +45082,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $2011万
@@ -45098,7 +45090,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1376万
@@ -45106,7 +45098,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1430万
@@ -45114,7 +45106,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1148万
@@ -45122,7 +45114,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1982万
@@ -45130,7 +45122,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1121万
@@ -45138,7 +45130,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $2028万
@@ -45146,7 +45138,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $2051万
@@ -45161,7 +45153,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1991万
@@ -45169,7 +45161,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1369万
@@ -45177,7 +45169,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1367万
@@ -45185,7 +45177,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1142万
@@ -45193,7 +45185,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $2011万
@@ -45201,7 +45193,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1161万
@@ -45209,7 +45201,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $2017万
@@ -45217,7 +45209,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1912万
@@ -45232,7 +45224,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $2070万
@@ -45240,7 +45232,7 @@
 (24年-06月-21日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1418万
@@ -45248,7 +45240,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1360万
@@ -45256,7 +45248,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1183万
@@ -45264,7 +45256,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $2001万
@@ -45272,7 +45264,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1156万
@@ -45280,7 +45272,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $2002万
@@ -45288,7 +45280,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1968万
@@ -45303,7 +45295,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $2032万
@@ -45311,7 +45303,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1398万
@@ -45319,7 +45311,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1395万
@@ -45327,7 +45319,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1167万
@@ -45335,7 +45327,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1991万
@@ -45343,7 +45335,7 @@
 (26年-03月-18日)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1150万
@@ -45351,7 +45343,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1986万
@@ -45359,7 +45351,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1943万
@@ -45374,7 +45366,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1933万
@@ -45382,7 +45374,7 @@
 (24年-05月-16日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1387万
@@ -45390,7 +45382,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1330万
@@ -45398,7 +45390,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1111万
@@ -45406,7 +45398,7 @@
 (24年-04月-06日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1981万
@@ -45414,7 +45406,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1140万
@@ -45422,7 +45414,7 @@
 (24年-04月-13日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1975万
@@ -45430,7 +45422,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1843万
@@ -45445,7 +45437,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1911万
@@ -45453,7 +45445,7 @@
 (24年-04月-13日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1375万
@@ -45461,7 +45453,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1318万
@@ -45469,7 +45461,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1142万
@@ -45477,7 +45469,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1971万
@@ -45485,7 +45477,7 @@
 (26年-03月-18日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1134万
@@ -45493,7 +45485,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1964万
@@ -45501,7 +45493,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1897万
@@ -45516,7 +45508,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1970万
@@ -45524,7 +45516,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1356万
@@ -45532,7 +45524,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1353万
@@ -45540,7 +45532,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1081万
@@ -45548,7 +45540,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $2238万
@@ -45556,7 +45548,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1128万
@@ -45564,7 +45556,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1944万
@@ -45572,7 +45564,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1878万
@@ -45587,7 +45579,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1960万
@@ -45595,7 +45587,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1285万
@@ -45603,7 +45595,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1336万
@@ -45611,7 +45603,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1116万
@@ -45619,7 +45611,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1896万
@@ -45627,7 +45619,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1123万
@@ -45635,7 +45627,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1926万
@@ -45643,7 +45635,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1787万
@@ -45658,7 +45650,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1873万
@@ -45666,7 +45658,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1326万
@@ -45674,7 +45666,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1323万
@@ -45682,7 +45674,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1066万
@@ -45690,7 +45682,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1870万
@@ -45698,7 +45690,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1073万
@@ -45706,7 +45698,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1909万
@@ -45714,7 +45706,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1770万
@@ -45729,7 +45721,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1864万
@@ -45737,7 +45729,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1277万
@@ -45745,7 +45737,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1306万
@@ -45753,7 +45745,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1069万
@@ -45761,7 +45753,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1772万
@@ -45769,7 +45761,7 @@
 (24年-04月-06日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1112万
@@ -45777,7 +45769,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1890万
@@ -45785,7 +45777,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1746万
@@ -45800,7 +45792,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1931万
@@ -45808,7 +45800,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1269万
@@ -45816,7 +45808,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1297万
@@ -45824,7 +45816,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1020万
@@ -45832,7 +45824,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1827万
@@ -45840,7 +45832,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1062万
@@ -45848,7 +45840,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1881万
@@ -45856,7 +45848,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1793万
@@ -45871,7 +45863,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1841万
@@ -45879,7 +45871,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1258万
@@ -45887,7 +45879,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1282万
@@ -45895,7 +45887,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1012万
@@ -45903,7 +45895,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1810万
@@ -45911,7 +45903,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1098万
@@ -45919,7 +45911,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1797万
@@ -45927,7 +45919,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1776万
@@ -45942,7 +45934,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1832万
@@ -45950,7 +45942,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1244万
@@ -45958,7 +45950,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1319万
@@ -45966,7 +45958,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1042万
@@ -45974,7 +45966,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1801万
@@ -45982,7 +45974,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1030万
@@ -45990,7 +45982,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1788万
@@ -45998,7 +45990,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1698万
@@ -46013,7 +46005,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1898万
@@ -46021,7 +46013,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1233万
@@ -46029,7 +46021,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1260万
@@ -46037,7 +46029,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1033万
@@ -46045,7 +46037,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1721万
@@ -46053,7 +46045,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1058万
@@ -46061,7 +46053,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1853万
@@ -46069,7 +46061,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1759万
@@ -46084,7 +46076,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1888万
@@ -46092,7 +46084,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1218万
@@ -46100,7 +46092,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1306万
@@ -46108,7 +46100,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $980万
@@ -46116,7 +46108,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1783万
@@ -46124,7 +46116,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1212万
@@ -46132,7 +46124,7 @@
 (26年-06月-05日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1844万
@@ -46140,7 +46132,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1750万
@@ -46155,7 +46147,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1876万
@@ -46163,7 +46155,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1155万
@@ -46171,7 +46163,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1299万
@@ -46179,7 +46171,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1007万
@@ -46187,7 +46179,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1774万
@@ -46195,7 +46187,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1041万
@@ -46203,7 +46195,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $2064万
@@ -46211,7 +46203,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1741万
@@ -46226,7 +46218,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1867万
@@ -46234,7 +46226,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1194万
@@ -46242,7 +46234,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1290万
@@ -46250,7 +46242,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $1000万
@@ -46258,7 +46250,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1766万
@@ -46266,7 +46258,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1034万
@@ -46274,7 +46266,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $2054万
@@ -46282,7 +46274,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1664万
@@ -46297,7 +46289,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1858万
@@ -46305,7 +46297,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1141万
@@ -46313,7 +46305,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1232万
@@ -46321,7 +46313,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $995万
@@ -46329,7 +46321,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1757万
@@ -46337,7 +46329,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $1016万
@@ -46345,7 +46337,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1816万
@@ -46353,7 +46345,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1724万
@@ -46368,7 +46360,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1775万
@@ -46376,7 +46368,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1135万
@@ -46384,7 +46376,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1277万
@@ -46392,7 +46384,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $990万
@@ -46400,7 +46392,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1748万
@@ -46408,7 +46400,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $998万
@@ -46416,7 +46408,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1807万
@@ -46424,7 +46416,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1715万
@@ -46439,7 +46431,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1830万
@@ -46447,7 +46439,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1176万
@@ -46455,7 +46447,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1218万
@@ -46463,7 +46455,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $946万
@@ -46471,7 +46463,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 792呎 (3房)
 $1739万
@@ -46479,7 +46471,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 454呎 (2房)
 $993万
@@ -46487,7 +46479,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
 $1789万
@@ -46495,7 +46487,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1698万
@@ -46510,7 +46502,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1816万
@@ -46518,7 +46510,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1170万
@@ -46526,7 +46518,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1572万
@@ -46534,7 +46526,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $980万
@@ -46542,7 +46534,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1664万
@@ -46551,7 +46543,7 @@
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr"/>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1772万
@@ -46559,7 +46551,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1690万
@@ -46574,7 +46566,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1808万
@@ -46582,7 +46574,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1118万
@@ -46590,7 +46582,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1256万
@@ -46598,7 +46590,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $975万
@@ -46606,7 +46598,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1655万
@@ -46615,7 +46607,7 @@
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr"/>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1693万
@@ -46623,7 +46615,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1681万
@@ -46638,7 +46630,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1798万
@@ -46646,7 +46638,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1159万
@@ -46654,7 +46646,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1197万
@@ -46662,7 +46654,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $970万
@@ -46670,7 +46662,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1715万
@@ -46679,7 +46671,7 @@
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr"/>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1685万
@@ -46687,7 +46679,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1673万
@@ -46702,7 +46694,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1790万
@@ -46710,7 +46702,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1153万
@@ -46718,7 +46710,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1240万
@@ -46726,7 +46718,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $965万
@@ -46734,7 +46726,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1706万
@@ -46743,7 +46735,7 @@
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1676万
@@ -46751,7 +46743,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1599万
@@ -46766,7 +46758,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1781万
@@ -46774,7 +46766,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1102万
@@ -46782,7 +46774,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1234万
@@ -46790,7 +46782,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $923万
@@ -46798,7 +46790,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1698万
@@ -46807,7 +46799,7 @@
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr"/>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1668万
@@ -46815,7 +46807,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1591万
@@ -46830,7 +46822,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1772万
@@ -46838,7 +46830,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1143万
@@ -46846,7 +46838,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1228万
@@ -46854,7 +46846,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $957万
@@ -46862,7 +46854,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1785万
@@ -46871,7 +46863,7 @@
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr"/>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1660万
@@ -46879,7 +46871,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1813万
@@ -46894,7 +46886,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1763万
@@ -46902,7 +46894,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1132万
@@ -46910,7 +46902,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1528万
@@ -46918,7 +46910,7 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $948万
@@ -46926,7 +46918,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1673万
@@ -46935,7 +46927,7 @@
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr"/>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1651万
@@ -46943,7 +46935,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1640万
@@ -46958,7 +46950,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1676万
@@ -46966,7 +46958,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1082万
@@ -46974,7 +46966,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1207万
@@ -46982,7 +46974,7 @@
 (24年-05月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $943万
@@ -46990,7 +46982,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1663万
@@ -46999,7 +46991,7 @@
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr"/>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1635万
@@ -47007,7 +46999,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1624万
@@ -47022,7 +47014,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1656万
@@ -47030,7 +47022,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1113万
@@ -47038,7 +47030,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1195万
@@ -47046,7 +47038,7 @@
 (24年-05月-06日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $932万
@@ -47054,7 +47046,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1642万
@@ -47063,7 +47055,7 @@
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr"/>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1619万
@@ -47071,7 +47063,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1608万
@@ -47086,7 +47078,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
 $1690万
@@ -47094,7 +47086,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 538呎 (2房)
 $1092万
@@ -47102,7 +47094,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 538呎 (2房)
 $1125万
@@ -47110,7 +47102,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 452呎 (2房)
 $914万
@@ -47118,7 +47110,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 813呎 (3房)
 $1544万
@@ -47127,7 +47119,7 @@
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr"/>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
 $1652万
@@ -47135,7 +47127,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>H | 746呎 (3房)
 $1576万

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -25167,7 +25167,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -44728,7 +44728,7 @@
           <t>B | 773呎 (3房)
 $2026万
 $26,210/呎
-(26年-07月-22日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -41090,7 +41090,7 @@
           <t>B | 1267呎 (4+房)
 $4029万
 $31,800/呎
-(26年-07月-22日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -40778,7 +40778,7 @@
           <t>B | 1267呎 (4+房)
 $4637万
 $36,600/呎
-(26年-07月-31日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -40770,7 +40770,7 @@
           <t>A | 1263呎 (4+房)
 $4825万
 $38,200/呎
-(26年-08月-03日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
